--- a/Team-Data/2008-09/11-4-2008-09.xlsx
+++ b/Team-Data/2008-09/11-4-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -760,19 +827,19 @@
         <v>2</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AM2" t="n">
         <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
         <v>25</v>
@@ -784,13 +851,13 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -799,13 +866,13 @@
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY2" t="n">
         <v>26</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA2" t="n">
         <v>16</v>
@@ -814,7 +881,7 @@
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -858,43 +925,43 @@
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>33</v>
+        <v>30.7</v>
       </c>
       <c r="J3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K3" t="n">
-        <v>0.434</v>
+        <v>0.409</v>
       </c>
       <c r="L3" t="n">
         <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>0.225</v>
+        <v>0.214</v>
       </c>
       <c r="O3" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="P3" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S3" t="n">
         <v>33.7</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0.703</v>
-      </c>
-      <c r="R3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.7</v>
-      </c>
       <c r="T3" t="n">
-        <v>49</v>
+        <v>45.7</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>15.3</v>
       </c>
       <c r="V3" t="n">
         <v>20.3</v>
@@ -903,22 +970,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>25.3</v>
+        <v>26.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>92.7</v>
+        <v>88.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="AD3" t="n">
         <v>10</v>
@@ -927,76 +994,76 @@
         <v>7</v>
       </c>
       <c r="AF3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
         <v>5</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AJ3" t="n">
         <v>24</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>26</v>
       </c>
       <c r="AM3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AV3" t="n">
         <v>30</v>
       </c>
       <c r="AW3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1176,7 @@
         <v>16</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>18</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>25</v>
@@ -1133,43 +1200,43 @@
         <v>27</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>9</v>
@@ -1178,7 +1245,7 @@
         <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -1207,160 +1274,160 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="J5" t="n">
-        <v>84.7</v>
+        <v>80.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.374</v>
+        <v>0.402</v>
       </c>
       <c r="L5" t="n">
         <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="N5" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="O5" t="n">
-        <v>21.3</v>
+        <v>24.3</v>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>30.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.821</v>
+        <v>0.795</v>
       </c>
       <c r="R5" t="n">
         <v>14</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>31.3</v>
       </c>
       <c r="T5" t="n">
-        <v>47</v>
+        <v>45.3</v>
       </c>
       <c r="U5" t="n">
-        <v>14.3</v>
+        <v>17.5</v>
       </c>
       <c r="V5" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="X5" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.7</v>
+        <v>22.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>89.7</v>
+        <v>94.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
       </c>
       <c r="AI5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK5" t="n">
         <v>28</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>30</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
       </c>
       <c r="AM5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU5" t="n">
         <v>24</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>29</v>
       </c>
       <c r="AV5" t="n">
         <v>28</v>
       </c>
       <c r="AW5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>18</v>
       </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>24</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BC5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -1389,160 +1456,160 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>35.3</v>
+        <v>33.8</v>
       </c>
       <c r="J6" t="n">
-        <v>75.3</v>
+        <v>73.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0.469</v>
+        <v>0.459</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.362</v>
+        <v>0.329</v>
       </c>
       <c r="O6" t="n">
-        <v>18.3</v>
+        <v>19.8</v>
       </c>
       <c r="P6" t="n">
-        <v>26.7</v>
+        <v>28.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.699</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="T6" t="n">
-        <v>44.7</v>
+        <v>43.8</v>
       </c>
       <c r="U6" t="n">
-        <v>21</v>
+        <v>19.8</v>
       </c>
       <c r="V6" t="n">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>22.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>96</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>7</v>
       </c>
       <c r="AF6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
         <v>5</v>
       </c>
       <c r="AI6" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
         <v>7</v>
       </c>
       <c r="AL6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AM6" t="n">
         <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA6" t="n">
         <v>13</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>17</v>
-      </c>
       <c r="BB6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -1571,160 +1638,160 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48</v>
       </c>
       <c r="I7" t="n">
-        <v>36</v>
+        <v>33.7</v>
       </c>
       <c r="J7" t="n">
-        <v>79.8</v>
+        <v>79.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0.451</v>
+        <v>0.424</v>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="M7" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="O7" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="P7" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29</v>
+      </c>
+      <c r="T7" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="W7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="n">
         <v>16</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="O7" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="R7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S7" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="U7" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="W7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>7</v>
-      </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AH7" t="n">
         <v>5</v>
       </c>
       <c r="AI7" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AJ7" t="n">
         <v>16</v>
       </c>
       <c r="AK7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AM7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR7" t="n">
         <v>24</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA7" t="n">
         <v>16</v>
       </c>
-      <c r="AV7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>22</v>
       </c>
-      <c r="BB7" t="n">
-        <v>19</v>
-      </c>
       <c r="BC7" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1904,7 @@
         <v>16</v>
       </c>
       <c r="AF8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>18</v>
@@ -1849,25 +1916,25 @@
         <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL8" t="n">
         <v>17</v>
       </c>
       <c r="AM8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
       </c>
       <c r="AO8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
         <v>17</v>
@@ -1876,28 +1943,28 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW8" t="n">
         <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY8" t="n">
         <v>16</v>
       </c>
       <c r="AZ8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA8" t="n">
         <v>5</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2037,16 +2104,16 @@
         <v>3</v>
       </c>
       <c r="AL9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM9" t="n">
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP9" t="n">
         <v>28</v>
@@ -2058,37 +2125,37 @@
         <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2201,7 +2268,7 @@
         <v>16</v>
       </c>
       <c r="AF10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
         <v>26</v>
@@ -2225,43 +2292,43 @@
         <v>3</v>
       </c>
       <c r="AN10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO10" t="n">
         <v>14</v>
       </c>
-      <c r="AO10" t="n">
-        <v>13</v>
-      </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR10" t="n">
         <v>4</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
         <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>6</v>
@@ -2270,7 +2337,7 @@
         <v>9</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2299,94 +2366,94 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>32</v>
+        <v>31.3</v>
       </c>
       <c r="J11" t="n">
-        <v>79.8</v>
+        <v>77.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.401</v>
+        <v>0.405</v>
       </c>
       <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>17</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="S11" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>46</v>
+      </c>
+      <c r="U11" t="n">
+        <v>17</v>
+      </c>
+      <c r="V11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="W11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y11" t="n">
         <v>6.3</v>
       </c>
-      <c r="M11" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O11" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="P11" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="Z11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="AC11" t="n">
         <v>11</v>
       </c>
-      <c r="S11" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="U11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="V11" t="n">
-        <v>13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.3</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
         <v>5</v>
@@ -2395,22 +2462,22 @@
         <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AK11" t="n">
         <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
         <v>11</v>
       </c>
       <c r="AO11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
         <v>7</v>
@@ -2419,40 +2486,40 @@
         <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AV11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2565,10 +2632,10 @@
         <v>16</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>5</v>
@@ -2577,7 +2644,7 @@
         <v>24</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK12" t="n">
         <v>15</v>
@@ -2586,16 +2653,16 @@
         <v>17</v>
       </c>
       <c r="AM12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2607,10 +2674,10 @@
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV12" t="n">
         <v>26</v>
@@ -2625,16 +2692,16 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
         <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2756,37 +2823,37 @@
         <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>14</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN13" t="n">
         <v>23</v>
       </c>
-      <c r="AM13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>24</v>
-      </c>
       <c r="AO13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP13" t="n">
         <v>19</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT13" t="n">
         <v>18</v>
@@ -2801,7 +2868,7 @@
         <v>24</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
@@ -2810,7 +2877,7 @@
         <v>27</v>
       </c>
       <c r="BA13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -2845,10 +2912,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2863,70 +2930,70 @@
         <v>37</v>
       </c>
       <c r="J14" t="n">
-        <v>83.5</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>0.443</v>
+        <v>0.451</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="M14" t="n">
-        <v>18</v>
+        <v>15.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>28.5</v>
+        <v>24</v>
       </c>
       <c r="P14" t="n">
-        <v>38</v>
+        <v>31.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.75</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="S14" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
       <c r="T14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U14" t="n">
-        <v>23</v>
+        <v>21.7</v>
       </c>
       <c r="V14" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="W14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>22</v>
+        <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>27.5</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>110.5</v>
+        <v>105.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
@@ -2941,31 +3008,31 @@
         <v>9</v>
       </c>
       <c r="AJ14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL14" t="n">
         <v>6</v>
       </c>
-      <c r="AK14" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3</v>
-      </c>
       <c r="AM14" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AN14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS14" t="n">
         <v>1</v>
@@ -2974,28 +3041,28 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
         <v>18</v>
       </c>
       <c r="AW14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX14" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -3111,10 +3178,10 @@
         <v>7</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH15" t="n">
         <v>5</v>
@@ -3123,7 +3190,7 @@
         <v>26</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
@@ -3135,19 +3202,19 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS15" t="n">
         <v>6</v>
@@ -3162,13 +3229,13 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
@@ -3180,7 +3247,7 @@
         <v>30</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3360,7 @@
         <v>16</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>18</v>
@@ -3308,34 +3375,34 @@
         <v>9</v>
       </c>
       <c r="AK16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN16" t="n">
         <v>17</v>
       </c>
       <c r="AO16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP16" t="n">
         <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS16" t="n">
         <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
         <v>12</v>
@@ -3347,7 +3414,7 @@
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>2</v>
@@ -3359,10 +3426,10 @@
         <v>3</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -3391,160 +3458,160 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
         <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>35.7</v>
+        <v>36</v>
       </c>
       <c r="J17" t="n">
-        <v>79.3</v>
+        <v>79</v>
       </c>
       <c r="K17" t="n">
-        <v>0.45</v>
+        <v>0.456</v>
       </c>
       <c r="L17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
         <v>14</v>
       </c>
       <c r="N17" t="n">
-        <v>0.333</v>
+        <v>0.357</v>
       </c>
       <c r="O17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="R17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V17" t="n">
         <v>17</v>
       </c>
-      <c r="P17" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="R17" t="n">
-        <v>11</v>
-      </c>
-      <c r="S17" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="V17" t="n">
-        <v>16.3</v>
-      </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.3</v>
+        <v>23.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>93</v>
+        <v>93.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>7</v>
       </c>
       <c r="AF17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
         <v>5</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AM17" t="n">
         <v>22</v>
       </c>
       <c r="AN17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP17" t="n">
         <v>21</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AQ17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS17" t="n">
         <v>17</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>9</v>
-      </c>
       <c r="AT17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AU17" t="n">
         <v>11</v>
       </c>
       <c r="AV17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW17" t="n">
         <v>20</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA17" t="n">
         <v>18</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>14</v>
       </c>
       <c r="BB17" t="n">
         <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3724,7 @@
         <v>16</v>
       </c>
       <c r="AF18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>18</v>
@@ -3666,13 +3733,13 @@
         <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
         <v>27</v>
@@ -3690,43 +3757,43 @@
         <v>27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU18" t="n">
         <v>12</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW18" t="n">
         <v>23</v>
       </c>
       <c r="AX18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ18" t="n">
         <v>11</v>
       </c>
       <c r="BA18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -3755,148 +3822,148 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>33.3</v>
+        <v>36</v>
       </c>
       <c r="J19" t="n">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.41</v>
+        <v>0.447</v>
       </c>
       <c r="L19" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>20.3</v>
+        <v>19.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.311</v>
+        <v>0.308</v>
       </c>
       <c r="O19" t="n">
-        <v>19.7</v>
+        <v>18</v>
       </c>
       <c r="P19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.819</v>
+        <v>0.783</v>
       </c>
       <c r="R19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="S19" t="n">
-        <v>28</v>
+        <v>30.5</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
+        <v>22</v>
+      </c>
+      <c r="V19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>31</v>
+      </c>
+      <c r="AA19" t="n">
         <v>20</v>
       </c>
-      <c r="V19" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="W19" t="n">
-        <v>8</v>
-      </c>
-      <c r="X19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>19.7</v>
-      </c>
       <c r="AB19" t="n">
-        <v>92.7</v>
+        <v>96</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8.699999999999999</v>
+        <v>1</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
       </c>
       <c r="AF19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK19" t="n">
         <v>14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>13</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT19" t="n">
         <v>17</v>
       </c>
-      <c r="AO19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>21</v>
-      </c>
       <c r="AU19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AV19" t="n">
         <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AX19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AZ19" t="n">
         <v>30</v>
@@ -3905,10 +3972,10 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4100,7 @@
         <v>5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK20" t="n">
         <v>4</v>
@@ -4042,16 +4109,16 @@
         <v>2</v>
       </c>
       <c r="AM20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
         <v>2</v>
       </c>
       <c r="AO20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ20" t="n">
         <v>12</v>
@@ -4060,7 +4127,7 @@
         <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4069,28 +4136,28 @@
         <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW20" t="n">
         <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA20" t="n">
         <v>4</v>
       </c>
       <c r="BB20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4270,7 @@
         <v>16</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG21" t="n">
         <v>18</v>
@@ -4212,13 +4279,13 @@
         <v>5</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ21" t="n">
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,28 +4297,28 @@
         <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ21" t="n">
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ21" t="n">
         <v>20</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
         <v>18</v>
@@ -4394,10 +4461,10 @@
         <v>5</v>
       </c>
       <c r="AI22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
         <v>23</v>
@@ -4412,7 +4479,7 @@
         <v>29</v>
       </c>
       <c r="AO22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP22" t="n">
         <v>25</v>
@@ -4421,13 +4488,13 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4442,10 +4509,10 @@
         <v>11</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA22" t="n">
         <v>29</v>
@@ -4454,7 +4521,7 @@
         <v>28</v>
       </c>
       <c r="BC22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4567,22 +4634,22 @@
         <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH23" t="n">
         <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>5</v>
@@ -4594,40 +4661,40 @@
         <v>19</v>
       </c>
       <c r="AO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ23" t="n">
         <v>26</v>
       </c>
       <c r="AR23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT23" t="n">
         <v>8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>27</v>
       </c>
       <c r="AV23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
         <v>10</v>
       </c>
       <c r="AX23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
         <v>6</v>
@@ -4636,7 +4703,7 @@
         <v>14</v>
       </c>
       <c r="BC23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4749,10 +4816,10 @@
         <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH24" t="n">
         <v>5</v>
@@ -4761,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="AJ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK24" t="n">
         <v>5</v>
@@ -4770,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="AM24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN24" t="n">
         <v>6</v>
@@ -4803,19 +4870,19 @@
         <v>28</v>
       </c>
       <c r="AX24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA24" t="n">
         <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
         <v>3</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -4847,100 +4914,100 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>39.3</v>
+        <v>38</v>
       </c>
       <c r="J25" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K25" t="n">
-        <v>0.553</v>
+        <v>0.528</v>
       </c>
       <c r="L25" t="n">
-        <v>7.8</v>
+        <v>6.3</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0.456</v>
+        <v>0.38</v>
       </c>
       <c r="O25" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="P25" t="n">
-        <v>25.3</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.733</v>
+        <v>0.744</v>
       </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="S25" t="n">
-        <v>32.3</v>
+        <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>38.3</v>
+        <v>37.7</v>
       </c>
       <c r="U25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="V25" t="n">
-        <v>16.5</v>
+        <v>15.3</v>
       </c>
       <c r="W25" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.8</v>
+        <v>101.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AF25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH25" t="n">
         <v>5</v>
       </c>
       <c r="AI25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ25" t="n">
         <v>29</v>
@@ -4949,13 +5016,13 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AM25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>17</v>
@@ -4964,31 +5031,31 @@
         <v>16</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX25" t="n">
         <v>23</v>
       </c>
-      <c r="AU25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>16</v>
-      </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>4</v>
@@ -4997,10 +5064,10 @@
         <v>19</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -5029,160 +5096,160 @@
         </is>
       </c>
       <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
       <c r="G26" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H26" t="n">
         <v>48</v>
       </c>
       <c r="I26" t="n">
-        <v>37.5</v>
+        <v>34.7</v>
       </c>
       <c r="J26" t="n">
-        <v>81.5</v>
+        <v>82.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.421</v>
       </c>
       <c r="L26" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="N26" t="n">
-        <v>0.385</v>
+        <v>0.397</v>
       </c>
       <c r="O26" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="P26" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="R26" t="n">
-        <v>11</v>
+        <v>11.7</v>
       </c>
       <c r="S26" t="n">
-        <v>21.5</v>
+        <v>24.7</v>
       </c>
       <c r="T26" t="n">
-        <v>32.5</v>
+        <v>36.3</v>
       </c>
       <c r="U26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="V26" t="n">
-        <v>8.5</v>
+        <v>10.3</v>
       </c>
       <c r="W26" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>21.5</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>98</v>
+        <v>90.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>16</v>
       </c>
       <c r="AF26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN26" t="n">
         <v>7</v>
       </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>8</v>
-      </c>
       <c r="AO26" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AP26" t="n">
         <v>29</v>
       </c>
       <c r="AQ26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW26" t="n">
         <v>8</v>
       </c>
-      <c r="AR26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU26" t="n">
+      <c r="AX26" t="n">
         <v>23</v>
       </c>
-      <c r="AV26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>22</v>
-      </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BA26" t="n">
         <v>30</v>
       </c>
       <c r="BB26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BC26" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -5304,43 +5371,43 @@
         <v>5</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ27" t="n">
         <v>23</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AN27" t="n">
         <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
         <v>27</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV27" t="n">
         <v>29</v>
@@ -5349,19 +5416,19 @@
         <v>25</v>
       </c>
       <c r="AX27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -5393,13 +5460,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -5408,76 +5475,76 @@
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
-        <v>73.3</v>
+        <v>74</v>
       </c>
       <c r="K28" t="n">
-        <v>0.491</v>
+        <v>0.527</v>
       </c>
       <c r="L28" t="n">
         <v>7</v>
       </c>
       <c r="M28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="P28" t="n">
         <v>17</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="O28" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="P28" t="n">
-        <v>18</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.759</v>
+        <v>0.794</v>
       </c>
       <c r="R28" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>27.7</v>
+        <v>28.5</v>
       </c>
       <c r="T28" t="n">
-        <v>34.3</v>
+        <v>34.5</v>
       </c>
       <c r="U28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V28" t="n">
-        <v>9.300000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="W28" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="Z28" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AA28" t="n">
         <v>19</v>
       </c>
-      <c r="AA28" t="n">
-        <v>17.7</v>
-      </c>
       <c r="AB28" t="n">
-        <v>92.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7.7</v>
+        <v>-3</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="AG28" t="n">
         <v>27</v>
@@ -5486,43 +5553,43 @@
         <v>5</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AJ28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP28" t="n">
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AR28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AT28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5534,19 +5601,19 @@
         <v>29</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="BA28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -5668,16 +5735,16 @@
         <v>1</v>
       </c>
       <c r="AI29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK29" t="n">
         <v>6</v>
       </c>
       <c r="AL29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM29" t="n">
         <v>20</v>
@@ -5686,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="AO29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
         <v>18</v>
@@ -5698,10 +5765,10 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>1</v>
@@ -5716,10 +5783,10 @@
         <v>4</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>14</v>
@@ -5728,7 +5795,7 @@
         <v>8</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -5853,10 +5920,10 @@
         <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL30" t="n">
         <v>29</v>
@@ -5868,40 +5935,40 @@
         <v>30</v>
       </c>
       <c r="AO30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AT30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW30" t="n">
         <v>4</v>
       </c>
       <c r="AX30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
         <v>9</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6090,7 @@
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>27</v>
@@ -6032,7 +6099,7 @@
         <v>5</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ31" t="n">
         <v>14</v>
@@ -6041,19 +6108,19 @@
         <v>16</v>
       </c>
       <c r="AL31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN31" t="n">
         <v>22</v>
       </c>
-      <c r="AM31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>23</v>
-      </c>
       <c r="AO31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ31" t="n">
         <v>11</v>
@@ -6062,16 +6129,16 @@
         <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AU31" t="n">
         <v>12</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW31" t="n">
         <v>25</v>
@@ -6083,7 +6150,7 @@
         <v>30</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>11</v>
@@ -6092,7 +6159,7 @@
         <v>12</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>11-4-2008-09</t>
+          <t>2008-11-04</t>
         </is>
       </c>
     </row>
